--- a/review-tasks/1g-load-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1g-load-review/jury/scoring-sheet.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Thread Group → ОП-10 Проверка по спискам финмониторинга → POST /api/v1/fm/check, «Use KeepAlive»</t>
+          <t>Thread Group → ОП-10 Проверка клиента по спискам финмониторинга → POST /api/v1/fm/check, «Use KeepAlive»</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Thread Group → ОП-10 Проверка по спискам финмониторинга → POST /api/v1/fm/check → Подпись, «Cache compiled script if available»</t>
+          <t>Thread Group → ОП-10 Проверка клиента по спискам финмониторинга → POST /api/v1/fm/check → Подпись, «Cache compiled script if available»</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Thread Group → ОП-10 Проверка по спискам финмониторинга → POST /api/v1/fm/check → Подпись, текст скрипта</t>
+          <t>Thread Group → ОП-10 Проверка клиента по спискам финмониторинга → POST /api/v1/fm/check → Подпись, текст скрипта</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Thread Group → ОП-10 Проверка по спискам финмониторинга → POST /api/v1/fm/check → Код 200</t>
+          <t>Thread Group → ОП-10 Проверка клиента по спискам финмониторинга → POST /api/v1/fm/check → Код 200</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>«Утечки нет», а нижняя граница heap (после сборки) выросла с 2,1 до 2,5 ГБ — на 18 % за 4 ч (рисунок 3). По 4.5 рост больше 10 % — утечка, тест не пройден</t>
+          <t>«Утечки нет», а нижняя граница heap (после сборки) выросла с 2,1 до 2,5 ГБ — на 17–18 % за 4 ч (рисунок 3). По 4.5 рост больше 10 % — утечка, тест не пройден</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Рекомендация «увеличить heap до 12 ГБ» не следует из данных: занято не больше 4,8 из 8 ГБ, нижняя граница ровная (рисунок 3). Методика 9.6</t>
+          <t>Рекомендация «увеличить heap до 12 ГБ» не следует из данных: занято не больше 4,4 из 8 ГБ, нижняя граница ровная (рисунок 3). Методика 9.6</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>строки 9–12</t>
+          <t>строки 10–15</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>строки 16–20</t>
+          <t>строки 18–23</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>строка 31</t>
+          <t>строка 34</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>строки 36–37</t>
+          <t>строки 39–40</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>строка 41</t>
+          <t>строка 44</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>строки 19, 22</t>
+          <t>строки 19–22</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>строка 26</t>
+          <t>строка 27</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>строка 26</t>
+          <t>строка 27</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>строки 4–7</t>
+          <t>строки 5–8</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
